--- a/data/datasets/test_all.xlsx
+++ b/data/datasets/test_all.xlsx
@@ -3330,10 +3330,10 @@
     </x:row>
     <x:row r="177">
       <x:c r="A177" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B177" t="s">
-        <x:v>294</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="C177" t="s">
         <x:v>244</x:v>
@@ -3341,10 +3341,10 @@
     </x:row>
     <x:row r="178">
       <x:c r="A178" t="s">
-        <x:v>356</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B178" t="s">
-        <x:v>357</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="C178" t="s">
         <x:v>244</x:v>
@@ -3352,10 +3352,10 @@
     </x:row>
     <x:row r="179">
       <x:c r="A179" t="s">
-        <x:v>358</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B179" t="s">
-        <x:v>359</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="C179" t="s">
         <x:v>244</x:v>
@@ -3363,10 +3363,10 @@
     </x:row>
     <x:row r="180">
       <x:c r="A180" t="s">
-        <x:v>360</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B180" t="s">
-        <x:v>361</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="C180" t="s">
         <x:v>244</x:v>
@@ -3374,10 +3374,10 @@
     </x:row>
     <x:row r="181">
       <x:c r="A181" t="s">
-        <x:v>362</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B181" t="s">
-        <x:v>363</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="C181" t="s">
         <x:v>244</x:v>
@@ -3385,10 +3385,10 @@
     </x:row>
     <x:row r="182">
       <x:c r="A182" t="s">
-        <x:v>364</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B182" t="s">
-        <x:v>365</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C182" t="s">
         <x:v>244</x:v>
@@ -3396,10 +3396,10 @@
     </x:row>
     <x:row r="183">
       <x:c r="A183" t="s">
-        <x:v>366</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B183" t="s">
-        <x:v>367</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="C183" t="s">
         <x:v>244</x:v>
@@ -3407,10 +3407,10 @@
     </x:row>
     <x:row r="184">
       <x:c r="A184" t="s">
-        <x:v>368</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B184" t="s">
-        <x:v>369</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="C184" t="s">
         <x:v>244</x:v>
@@ -3418,10 +3418,10 @@
     </x:row>
     <x:row r="185">
       <x:c r="A185" t="s">
-        <x:v>370</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B185" t="s">
-        <x:v>371</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="C185" t="s">
         <x:v>244</x:v>
@@ -3429,43 +3429,43 @@
     </x:row>
     <x:row r="186">
       <x:c r="A186" t="s">
-        <x:v>372</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B186" t="s">
-        <x:v>361</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="C186" t="s">
         <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="B187" t="s">
-        <x:v>374</x:v>
-      </x:c>
-      <x:c r="C187" t="s">
-        <x:v>244</x:v>
+      <x:c r="A187" t="str">
+        <x:v>y=4242x-3794x^{2}-3573x^{3}+4913x^{4}-3952x^{5}-4159x^{6}+2551x^{7}+3764x^{8}+C</x:v>
+      </x:c>
+      <x:c r="B187" t="str">
+        <x:v>y^{\prime}=4242-7588x-10719x^{2}+19652x^{3}-19760x^{4}-24954x^{5}+17857x^{6}+30112x^{7}</x:v>
+      </x:c>
+      <x:c r="C187" t="str">
+        <x:v>polynomial</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="B188" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="C188" t="s">
-        <x:v>244</x:v>
+      <x:c r="A188" t="str">
+        <x:v>y=-3670x-454x^{2}+3978x^{3}-1026x^{4}+2082x^{5}-4037x^{6}+C</x:v>
+      </x:c>
+      <x:c r="B188" t="str">
+        <x:v>y^{\prime}=-3670-908x+11934x^{2}-4104x^{3}+10410x^{4}-24222x^{5}</x:v>
+      </x:c>
+      <x:c r="C188" t="str">
+        <x:v>polynomial</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" t="str">
-        <x:v>y=4242x-3794x^{2}-3573x^{3}+4913x^{4}-3952x^{5}-4159x^{6}+2551x^{7}+3764x^{8}+C</x:v>
+        <x:v>y=1072x+3740x^{2}-2415x^{3}+3546x^{4}-1550x^{5}+4729x^{6}+176x^{7}+C</x:v>
       </x:c>
       <x:c r="B189" t="str">
-        <x:v>y^{\prime}=4242-7588x-10719x^{2}+19652x^{3}-19760x^{4}-24954x^{5}+17857x^{6}+30112x^{7}</x:v>
+        <x:v>y^{\prime}=1072+7480x-7245x^{2}+14184x^{3}-7750x^{4}+28374x^{5}+1232x^{6}</x:v>
       </x:c>
       <x:c r="C189" t="str">
         <x:v>polynomial</x:v>
@@ -3473,10 +3473,10 @@
     </x:row>
     <x:row r="190">
       <x:c r="A190" t="str">
-        <x:v>y=-3670x-454x^{2}+3978x^{3}-1026x^{4}+2082x^{5}-4037x^{6}+C</x:v>
+        <x:v>y=-4277x+2732x^{2}+4004x^{3}+C</x:v>
       </x:c>
       <x:c r="B190" t="str">
-        <x:v>y^{\prime}=-3670-908x+11934x^{2}-4104x^{3}+10410x^{4}-24222x^{5}</x:v>
+        <x:v>y^{\prime}=-4277+5464x+12012x^{2}</x:v>
       </x:c>
       <x:c r="C190" t="str">
         <x:v>polynomial</x:v>
@@ -3484,10 +3484,10 @@
     </x:row>
     <x:row r="191">
       <x:c r="A191" t="str">
-        <x:v>y=1072x+3740x^{2}-2415x^{3}+3546x^{4}-1550x^{5}+4729x^{6}+176x^{7}+C</x:v>
+        <x:v>y=-117x-1330x^{2}-4612x^{3}-745x^{4}-3617x^{5}-490x^{6}+C</x:v>
       </x:c>
       <x:c r="B191" t="str">
-        <x:v>y^{\prime}=1072+7480x-7245x^{2}+14184x^{3}-7750x^{4}+28374x^{5}+1232x^{6}</x:v>
+        <x:v>y^{\prime}=-117-2660x-13836x^{2}-2980x^{3}-18085x^{4}-2940x^{5}</x:v>
       </x:c>
       <x:c r="C191" t="str">
         <x:v>polynomial</x:v>
@@ -3495,10 +3495,10 @@
     </x:row>
     <x:row r="192">
       <x:c r="A192" t="str">
-        <x:v>y=-4277x+2732x^{2}+4004x^{3}+C</x:v>
+        <x:v>y=-2775x-1602x^{2}+1079x^{3}+3359x^{4}-1239x^{5}+785x^{6}+1173x^{7}+C</x:v>
       </x:c>
       <x:c r="B192" t="str">
-        <x:v>y^{\prime}=-4277+5464x+12012x^{2}</x:v>
+        <x:v>y^{\prime}=-2775-3204x+3237x^{2}+13436x^{3}-6195x^{4}+4710x^{5}+8211x^{6}</x:v>
       </x:c>
       <x:c r="C192" t="str">
         <x:v>polynomial</x:v>
@@ -3506,10 +3506,10 @@
     </x:row>
     <x:row r="193">
       <x:c r="A193" t="str">
-        <x:v>y=-117x-1330x^{2}-4612x^{3}-745x^{4}-3617x^{5}-490x^{6}+C</x:v>
+        <x:v>y=-3999x-4841x^{2}-1225x^{3}-2180x^{4}+1023x^{5}+2164x^{6}+C</x:v>
       </x:c>
       <x:c r="B193" t="str">
-        <x:v>y^{\prime}=-117-2660x-13836x^{2}-2980x^{3}-18085x^{4}-2940x^{5}</x:v>
+        <x:v>y^{\prime}=-3999-9682x-3675x^{2}-8720x^{3}+5115x^{4}+12984x^{5}</x:v>
       </x:c>
       <x:c r="C193" t="str">
         <x:v>polynomial</x:v>
@@ -3517,10 +3517,10 @@
     </x:row>
     <x:row r="194">
       <x:c r="A194" t="str">
-        <x:v>y=-2775x-1602x^{2}+1079x^{3}+3359x^{4}-1239x^{5}+785x^{6}+1173x^{7}+C</x:v>
+        <x:v>y=-2074x-2672x^{2}-4015x^{3}-3445x^{4}-715x^{5}-233x^{6}+4399x^{7}+C</x:v>
       </x:c>
       <x:c r="B194" t="str">
-        <x:v>y^{\prime}=-2775-3204x+3237x^{2}+13436x^{3}-6195x^{4}+4710x^{5}+8211x^{6}</x:v>
+        <x:v>y^{\prime}=-2074-5344x-12045x^{2}-13780x^{3}-3575x^{4}-1398x^{5}+30793x^{6}</x:v>
       </x:c>
       <x:c r="C194" t="str">
         <x:v>polynomial</x:v>
@@ -3528,10 +3528,10 @@
     </x:row>
     <x:row r="195">
       <x:c r="A195" t="str">
-        <x:v>y=-3999x-4841x^{2}-1225x^{3}-2180x^{4}+1023x^{5}+2164x^{6}+C</x:v>
+        <x:v>y=4538x+538x^{2}+2305x^{3}+1189x^{4}+2361x^{5}-2040x^{6}-2453x^{7}-2658x^{8}+C</x:v>
       </x:c>
       <x:c r="B195" t="str">
-        <x:v>y^{\prime}=-3999-9682x-3675x^{2}-8720x^{3}+5115x^{4}+12984x^{5}</x:v>
+        <x:v>y^{\prime}=4538+1076x+6915x^{2}+4756x^{3}+11805x^{4}-12240x^{5}-17171x^{6}-21264x^{7}</x:v>
       </x:c>
       <x:c r="C195" t="str">
         <x:v>polynomial</x:v>
@@ -3539,10 +3539,10 @@
     </x:row>
     <x:row r="196">
       <x:c r="A196" t="str">
-        <x:v>y=-2074x-2672x^{2}-4015x^{3}-3445x^{4}-715x^{5}-233x^{6}+4399x^{7}+C</x:v>
+        <x:v>y=-158x+3385x^{2}-1350x^{3}-4492x^{4}-2430x^{5}+C</x:v>
       </x:c>
       <x:c r="B196" t="str">
-        <x:v>y^{\prime}=-2074-5344x-12045x^{2}-13780x^{3}-3575x^{4}-1398x^{5}+30793x^{6}</x:v>
+        <x:v>y^{\prime}=-158+6770x-4050x^{2}-17968x^{3}-12150x^{4}</x:v>
       </x:c>
       <x:c r="C196" t="str">
         <x:v>polynomial</x:v>
@@ -3550,10 +3550,10 @@
     </x:row>
     <x:row r="197">
       <x:c r="A197" t="str">
-        <x:v>y=4538x+538x^{2}+2305x^{3}+1189x^{4}+2361x^{5}-2040x^{6}-2453x^{7}-2658x^{8}+C</x:v>
+        <x:v>y=2961x-4541x^{2}-566x^{3}+2001x^{4}-1546x^{5}-545x^{6}+397x^{7}-593x^{8}+C</x:v>
       </x:c>
       <x:c r="B197" t="str">
-        <x:v>y^{\prime}=4538+1076x+6915x^{2}+4756x^{3}+11805x^{4}-12240x^{5}-17171x^{6}-21264x^{7}</x:v>
+        <x:v>y^{\prime}=2961-9082x-1698x^{2}+8004x^{3}-7730x^{4}-3270x^{5}+2779x^{6}-4744x^{7}</x:v>
       </x:c>
       <x:c r="C197" t="str">
         <x:v>polynomial</x:v>
@@ -3561,10 +3561,10 @@
     </x:row>
     <x:row r="198">
       <x:c r="A198" t="str">
-        <x:v>y=-158x+3385x^{2}-1350x^{3}-4492x^{4}-2430x^{5}+C</x:v>
+        <x:v>y=-1118x+923x^{2}-4485x^{3}-1269x^{4}+3950x^{5}+1892x^{6}+2905x^{7}-4006x^{8}+C</x:v>
       </x:c>
       <x:c r="B198" t="str">
-        <x:v>y^{\prime}=-158+6770x-4050x^{2}-17968x^{3}-12150x^{4}</x:v>
+        <x:v>y^{\prime}=-1118+1846x-13455x^{2}-5076x^{3}+19750x^{4}+11352x^{5}+20335x^{6}-32048x^{7}</x:v>
       </x:c>
       <x:c r="C198" t="str">
         <x:v>polynomial</x:v>
@@ -3572,10 +3572,10 @@
     </x:row>
     <x:row r="199">
       <x:c r="A199" t="str">
-        <x:v>y=2961x-4541x^{2}-566x^{3}+2001x^{4}-1546x^{5}-545x^{6}+397x^{7}-593x^{8}+C</x:v>
+        <x:v>y=816x-64x^{2}-2247x^{3}-640x^{4}+C</x:v>
       </x:c>
       <x:c r="B199" t="str">
-        <x:v>y^{\prime}=2961-9082x-1698x^{2}+8004x^{3}-7730x^{4}-3270x^{5}+2779x^{6}-4744x^{7}</x:v>
+        <x:v>y^{\prime}=816-128x-6741x^{2}-2560x^{3}</x:v>
       </x:c>
       <x:c r="C199" t="str">
         <x:v>polynomial</x:v>
@@ -3583,10 +3583,10 @@
     </x:row>
     <x:row r="200">
       <x:c r="A200" t="str">
-        <x:v>y=-1118x+923x^{2}-4485x^{3}-1269x^{4}+3950x^{5}+1892x^{6}+2905x^{7}-4006x^{8}+C</x:v>
+        <x:v>y=-3398x-1875x^{2}-1241x^{3}+3857x^{4}+3837x^{5}+C</x:v>
       </x:c>
       <x:c r="B200" t="str">
-        <x:v>y^{\prime}=-1118+1846x-13455x^{2}-5076x^{3}+19750x^{4}+11352x^{5}+20335x^{6}-32048x^{7}</x:v>
+        <x:v>y^{\prime}=-3398-3750x-3723x^{2}+15428x^{3}+19185x^{4}</x:v>
       </x:c>
       <x:c r="C200" t="str">
         <x:v>polynomial</x:v>
@@ -3594,10 +3594,10 @@
     </x:row>
     <x:row r="201">
       <x:c r="A201" t="str">
-        <x:v>y=816x-64x^{2}-2247x^{3}-640x^{4}+C</x:v>
+        <x:v>y=1576x-2689x^{2}-3520x^{3}+1049x^{4}-1038x^{5}+452x^{6}-4695x^{7}+2114x^{8}+C</x:v>
       </x:c>
       <x:c r="B201" t="str">
-        <x:v>y^{\prime}=816-128x-6741x^{2}-2560x^{3}</x:v>
+        <x:v>y^{\prime}=1576-5378x-10560x^{2}+4196x^{3}-5190x^{4}+2712x^{5}-32865x^{6}+16912x^{7}</x:v>
       </x:c>
       <x:c r="C201" t="str">
         <x:v>polynomial</x:v>
@@ -3605,10 +3605,10 @@
     </x:row>
     <x:row r="202">
       <x:c r="A202" t="str">
-        <x:v>y=-3398x-1875x^{2}-1241x^{3}+3857x^{4}+3837x^{5}+C</x:v>
+        <x:v>y=2915x-117x^{2}-3524x^{3}-3268x^{4}+3240x^{5}+2896x^{6}+2011x^{7}-2280x^{8}+C</x:v>
       </x:c>
       <x:c r="B202" t="str">
-        <x:v>y^{\prime}=-3398-3750x-3723x^{2}+15428x^{3}+19185x^{4}</x:v>
+        <x:v>y^{\prime}=2915-234x-10572x^{2}-13072x^{3}+16200x^{4}+17376x^{5}+14077x^{6}-18240x^{7}</x:v>
       </x:c>
       <x:c r="C202" t="str">
         <x:v>polynomial</x:v>
@@ -3616,10 +3616,10 @@
     </x:row>
     <x:row r="203">
       <x:c r="A203" t="str">
-        <x:v>y=1576x-2689x^{2}-3520x^{3}+1049x^{4}-1038x^{5}+452x^{6}-4695x^{7}+2114x^{8}+C</x:v>
+        <x:v>y=-1837x+4915x^{2}+2657x^{3}+616x^{4}+14x^{5}+C</x:v>
       </x:c>
       <x:c r="B203" t="str">
-        <x:v>y^{\prime}=1576-5378x-10560x^{2}+4196x^{3}-5190x^{4}+2712x^{5}-32865x^{6}+16912x^{7}</x:v>
+        <x:v>y^{\prime}=-1837+9830x+7971x^{2}+2464x^{3}+70x^{4}</x:v>
       </x:c>
       <x:c r="C203" t="str">
         <x:v>polynomial</x:v>
@@ -3627,10 +3627,10 @@
     </x:row>
     <x:row r="204">
       <x:c r="A204" t="str">
-        <x:v>y=2915x-117x^{2}-3524x^{3}-3268x^{4}+3240x^{5}+2896x^{6}+2011x^{7}-2280x^{8}+C</x:v>
+        <x:v>y=1600x+2400x^{2}-981x^{3}+2104x^{4}+1481x^{5}+1403x^{6}+C</x:v>
       </x:c>
       <x:c r="B204" t="str">
-        <x:v>y^{\prime}=2915-234x-10572x^{2}-13072x^{3}+16200x^{4}+17376x^{5}+14077x^{6}-18240x^{7}</x:v>
+        <x:v>y^{\prime}=1600+4800x-2943x^{2}+8416x^{3}+7405x^{4}+8418x^{5}</x:v>
       </x:c>
       <x:c r="C204" t="str">
         <x:v>polynomial</x:v>
@@ -3638,10 +3638,10 @@
     </x:row>
     <x:row r="205">
       <x:c r="A205" t="str">
-        <x:v>y=-1837x+4915x^{2}+2657x^{3}+616x^{4}+14x^{5}+C</x:v>
+        <x:v>y=4116x-3834x^{2}+3206x^{3}-1426x^{4}+4774x^{5}-4002x^{6}+9x^{7}+C</x:v>
       </x:c>
       <x:c r="B205" t="str">
-        <x:v>y^{\prime}=-1837+9830x+7971x^{2}+2464x^{3}+70x^{4}</x:v>
+        <x:v>y^{\prime}=4116-7668x+9618x^{2}-5704x^{3}+23870x^{4}-24012x^{5}+63x^{6}</x:v>
       </x:c>
       <x:c r="C205" t="str">
         <x:v>polynomial</x:v>
@@ -3649,10 +3649,10 @@
     </x:row>
     <x:row r="206">
       <x:c r="A206" t="str">
-        <x:v>y=1600x+2400x^{2}-981x^{3}+2104x^{4}+1481x^{5}+1403x^{6}+C</x:v>
+        <x:v>y=3111x-2647x^{2}+C</x:v>
       </x:c>
       <x:c r="B206" t="str">
-        <x:v>y^{\prime}=1600+4800x-2943x^{2}+8416x^{3}+7405x^{4}+8418x^{5}</x:v>
+        <x:v>y^{\prime}=3111-5294x</x:v>
       </x:c>
       <x:c r="C206" t="str">
         <x:v>polynomial</x:v>
@@ -3660,10 +3660,10 @@
     </x:row>
     <x:row r="207">
       <x:c r="A207" t="str">
-        <x:v>y=4116x-3834x^{2}+3206x^{3}-1426x^{4}+4774x^{5}-4002x^{6}+9x^{7}+C</x:v>
+        <x:v>y=-221x-3419x^{2}+4877x^{3}+1158x^{4}-531x^{5}-576x^{6}+C</x:v>
       </x:c>
       <x:c r="B207" t="str">
-        <x:v>y^{\prime}=4116-7668x+9618x^{2}-5704x^{3}+23870x^{4}-24012x^{5}+63x^{6}</x:v>
+        <x:v>y^{\prime}=-221-6838x+14631x^{2}+4632x^{3}-2655x^{4}-3456x^{5}</x:v>
       </x:c>
       <x:c r="C207" t="str">
         <x:v>polynomial</x:v>
@@ -3671,10 +3671,10 @@
     </x:row>
     <x:row r="208">
       <x:c r="A208" t="str">
-        <x:v>y=3111x-2647x^{2}+C</x:v>
+        <x:v>y=-2567x-1517x^{2}-1262x^{3}-4735x^{4}+C</x:v>
       </x:c>
       <x:c r="B208" t="str">
-        <x:v>y^{\prime}=3111-5294x</x:v>
+        <x:v>y^{\prime}=-2567-3034x-3786x^{2}-18940x^{3}</x:v>
       </x:c>
       <x:c r="C208" t="str">
         <x:v>polynomial</x:v>
@@ -3682,10 +3682,10 @@
     </x:row>
     <x:row r="209">
       <x:c r="A209" t="str">
-        <x:v>y=-221x-3419x^{2}+4877x^{3}+1158x^{4}-531x^{5}-576x^{6}+C</x:v>
+        <x:v>y=-408x-4460x^{2}+4240x^{3}+3293x^{4}+C</x:v>
       </x:c>
       <x:c r="B209" t="str">
-        <x:v>y^{\prime}=-221-6838x+14631x^{2}+4632x^{3}-2655x^{4}-3456x^{5}</x:v>
+        <x:v>y^{\prime}=-408-8920x+12720x^{2}+13172x^{3}</x:v>
       </x:c>
       <x:c r="C209" t="str">
         <x:v>polynomial</x:v>
@@ -3693,10 +3693,10 @@
     </x:row>
     <x:row r="210">
       <x:c r="A210" t="str">
-        <x:v>y=-2567x-1517x^{2}-1262x^{3}-4735x^{4}+C</x:v>
+        <x:v>y=-2934x-3507x^{2}+C</x:v>
       </x:c>
       <x:c r="B210" t="str">
-        <x:v>y^{\prime}=-2567-3034x-3786x^{2}-18940x^{3}</x:v>
+        <x:v>y^{\prime}=-2934-7014x</x:v>
       </x:c>
       <x:c r="C210" t="str">
         <x:v>polynomial</x:v>
@@ -3704,10 +3704,10 @@
     </x:row>
     <x:row r="211">
       <x:c r="A211" t="str">
-        <x:v>y=-408x-4460x^{2}+4240x^{3}+3293x^{4}+C</x:v>
+        <x:v>y=-2077x-2021x^{2}+C</x:v>
       </x:c>
       <x:c r="B211" t="str">
-        <x:v>y^{\prime}=-408-8920x+12720x^{2}+13172x^{3}</x:v>
+        <x:v>y^{\prime}=-2077-4042x</x:v>
       </x:c>
       <x:c r="C211" t="str">
         <x:v>polynomial</x:v>
@@ -3715,10 +3715,10 @@
     </x:row>
     <x:row r="212">
       <x:c r="A212" t="str">
-        <x:v>y=-2934x-3507x^{2}+C</x:v>
+        <x:v>y=2336x+272x^{2}+120x^{3}+3471x^{4}-3338x^{5}-3528x^{6}+C</x:v>
       </x:c>
       <x:c r="B212" t="str">
-        <x:v>y^{\prime}=-2934-7014x</x:v>
+        <x:v>y^{\prime}=2336+544x+360x^{2}+13884x^{3}-16690x^{4}-21168x^{5}</x:v>
       </x:c>
       <x:c r="C212" t="str">
         <x:v>polynomial</x:v>
@@ -3726,10 +3726,10 @@
     </x:row>
     <x:row r="213">
       <x:c r="A213" t="str">
-        <x:v>y=-2077x-2021x^{2}+C</x:v>
+        <x:v>y=4265x-748x^{2}-183x^{3}-685x^{4}-2441x^{5}+4177x^{6}-3258x^{7}+C</x:v>
       </x:c>
       <x:c r="B213" t="str">
-        <x:v>y^{\prime}=-2077-4042x</x:v>
+        <x:v>y^{\prime}=4265-1496x-549x^{2}-2740x^{3}-12205x^{4}+25062x^{5}-22806x^{6}</x:v>
       </x:c>
       <x:c r="C213" t="str">
         <x:v>polynomial</x:v>
@@ -3737,10 +3737,10 @@
     </x:row>
     <x:row r="214">
       <x:c r="A214" t="str">
-        <x:v>y=2336x+272x^{2}+120x^{3}+3471x^{4}-3338x^{5}-3528x^{6}+C</x:v>
+        <x:v>y=-2776x-2312x^{2}-1805x^{3}+C</x:v>
       </x:c>
       <x:c r="B214" t="str">
-        <x:v>y^{\prime}=2336+544x+360x^{2}+13884x^{3}-16690x^{4}-21168x^{5}</x:v>
+        <x:v>y^{\prime}=-2776-4624x-5415x^{2}</x:v>
       </x:c>
       <x:c r="C214" t="str">
         <x:v>polynomial</x:v>
@@ -3748,10 +3748,10 @@
     </x:row>
     <x:row r="215">
       <x:c r="A215" t="str">
-        <x:v>y=4265x-748x^{2}-183x^{3}-685x^{4}-2441x^{5}+4177x^{6}-3258x^{7}+C</x:v>
+        <x:v>y=-1876x+351x^{2}-2728x^{3}-3597x^{4}+3096x^{5}+1247x^{6}+C</x:v>
       </x:c>
       <x:c r="B215" t="str">
-        <x:v>y^{\prime}=4265-1496x-549x^{2}-2740x^{3}-12205x^{4}+25062x^{5}-22806x^{6}</x:v>
+        <x:v>y^{\prime}=-1876+702x-8184x^{2}-14388x^{3}+15480x^{4}+7482x^{5}</x:v>
       </x:c>
       <x:c r="C215" t="str">
         <x:v>polynomial</x:v>
@@ -3759,10 +3759,10 @@
     </x:row>
     <x:row r="216">
       <x:c r="A216" t="str">
-        <x:v>y=-2776x-2312x^{2}-1805x^{3}+C</x:v>
+        <x:v>y=3623x-4860x^{2}+C</x:v>
       </x:c>
       <x:c r="B216" t="str">
-        <x:v>y^{\prime}=-2776-4624x-5415x^{2}</x:v>
+        <x:v>y^{\prime}=3623-9720x</x:v>
       </x:c>
       <x:c r="C216" t="str">
         <x:v>polynomial</x:v>
@@ -3770,10 +3770,10 @@
     </x:row>
     <x:row r="217">
       <x:c r="A217" t="str">
-        <x:v>y=-1876x+351x^{2}-2728x^{3}-3597x^{4}+3096x^{5}+1247x^{6}+C</x:v>
+        <x:v>y=264x+3515x^{2}+C</x:v>
       </x:c>
       <x:c r="B217" t="str">
-        <x:v>y^{\prime}=-1876+702x-8184x^{2}-14388x^{3}+15480x^{4}+7482x^{5}</x:v>
+        <x:v>y^{\prime}=264+7030x</x:v>
       </x:c>
       <x:c r="C217" t="str">
         <x:v>polynomial</x:v>
@@ -3781,10 +3781,10 @@
     </x:row>
     <x:row r="218">
       <x:c r="A218" t="str">
-        <x:v>y=3623x-4860x^{2}+C</x:v>
+        <x:v>y=-3256x-909x^{2}-1770x^{3}+1006x^{4}+3684x^{5}+2339x^{6}+2906x^{7}+C</x:v>
       </x:c>
       <x:c r="B218" t="str">
-        <x:v>y^{\prime}=3623-9720x</x:v>
+        <x:v>y^{\prime}=-3256-1818x-5310x^{2}+4024x^{3}+18420x^{4}+14034x^{5}+20342x^{6}</x:v>
       </x:c>
       <x:c r="C218" t="str">
         <x:v>polynomial</x:v>
@@ -3792,10 +3792,10 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" t="str">
-        <x:v>y=264x+3515x^{2}+C</x:v>
+        <x:v>y=-3483x+2182x^{2}+C</x:v>
       </x:c>
       <x:c r="B219" t="str">
-        <x:v>y^{\prime}=264+7030x</x:v>
+        <x:v>y^{\prime}=-3483+4364x</x:v>
       </x:c>
       <x:c r="C219" t="str">
         <x:v>polynomial</x:v>
@@ -3803,10 +3803,10 @@
     </x:row>
     <x:row r="220">
       <x:c r="A220" t="str">
-        <x:v>y=-3256x-909x^{2}-1770x^{3}+1006x^{4}+3684x^{5}+2339x^{6}+2906x^{7}+C</x:v>
+        <x:v>y=-4371x+4309x^{2}+C</x:v>
       </x:c>
       <x:c r="B220" t="str">
-        <x:v>y^{\prime}=-3256-1818x-5310x^{2}+4024x^{3}+18420x^{4}+14034x^{5}+20342x^{6}</x:v>
+        <x:v>y^{\prime}=-4371+8618x</x:v>
       </x:c>
       <x:c r="C220" t="str">
         <x:v>polynomial</x:v>
@@ -3814,10 +3814,10 @@
     </x:row>
     <x:row r="221">
       <x:c r="A221" t="str">
-        <x:v>y=-3483x+2182x^{2}+C</x:v>
+        <x:v>y=4479x+4099x^{2}-1346x^{3}+2161x^{4}+2351x^{5}-4797x^{6}+C</x:v>
       </x:c>
       <x:c r="B221" t="str">
-        <x:v>y^{\prime}=-3483+4364x</x:v>
+        <x:v>y^{\prime}=4479+8198x-4038x^{2}+8644x^{3}+11755x^{4}-28782x^{5}</x:v>
       </x:c>
       <x:c r="C221" t="str">
         <x:v>polynomial</x:v>
@@ -3825,10 +3825,10 @@
     </x:row>
     <x:row r="222">
       <x:c r="A222" t="str">
-        <x:v>y=-4371x+4309x^{2}+C</x:v>
+        <x:v>y=-1766x+3170x^{2}-3345x^{3}-1088x^{4}-3517x^{5}+1359x^{6}+1499x^{7}+C</x:v>
       </x:c>
       <x:c r="B222" t="str">
-        <x:v>y^{\prime}=-4371+8618x</x:v>
+        <x:v>y^{\prime}=-1766+6340x-10035x^{2}-4352x^{3}-17585x^{4}+8154x^{5}+10493x^{6}</x:v>
       </x:c>
       <x:c r="C222" t="str">
         <x:v>polynomial</x:v>
@@ -3836,10 +3836,10 @@
     </x:row>
     <x:row r="223">
       <x:c r="A223" t="str">
-        <x:v>y=4479x+4099x^{2}-1346x^{3}+2161x^{4}+2351x^{5}-4797x^{6}+C</x:v>
+        <x:v>y=1337x-2458x^{2}-787x^{3}+3939x^{4}+1827x^{5}-4765x^{6}+C</x:v>
       </x:c>
       <x:c r="B223" t="str">
-        <x:v>y^{\prime}=4479+8198x-4038x^{2}+8644x^{3}+11755x^{4}-28782x^{5}</x:v>
+        <x:v>y^{\prime}=1337-4916x-2361x^{2}+15756x^{3}+9135x^{4}-28590x^{5}</x:v>
       </x:c>
       <x:c r="C223" t="str">
         <x:v>polynomial</x:v>
@@ -3847,10 +3847,10 @@
     </x:row>
     <x:row r="224">
       <x:c r="A224" t="str">
-        <x:v>y=-1766x+3170x^{2}-3345x^{3}-1088x^{4}-3517x^{5}+1359x^{6}+1499x^{7}+C</x:v>
+        <x:v>y=-1851x+4155x^{2}-2495x^{3}+3816x^{4}-653x^{5}-2598x^{6}+C</x:v>
       </x:c>
       <x:c r="B224" t="str">
-        <x:v>y^{\prime}=-1766+6340x-10035x^{2}-4352x^{3}-17585x^{4}+8154x^{5}+10493x^{6}</x:v>
+        <x:v>y^{\prime}=-1851+8310x-7485x^{2}+15264x^{3}-3265x^{4}-15588x^{5}</x:v>
       </x:c>
       <x:c r="C224" t="str">
         <x:v>polynomial</x:v>
@@ -3858,10 +3858,10 @@
     </x:row>
     <x:row r="225">
       <x:c r="A225" t="str">
-        <x:v>y=1337x-2458x^{2}-787x^{3}+3939x^{4}+1827x^{5}-4765x^{6}+C</x:v>
+        <x:v>y=-3584x-4033x^{2}+4046x^{3}+1027x^{4}-4897x^{5}-4431x^{6}-3779x^{7}+C</x:v>
       </x:c>
       <x:c r="B225" t="str">
-        <x:v>y^{\prime}=1337-4916x-2361x^{2}+15756x^{3}+9135x^{4}-28590x^{5}</x:v>
+        <x:v>y^{\prime}=-3584-8066x+12138x^{2}+4108x^{3}-24485x^{4}-26586x^{5}-26453x^{6}</x:v>
       </x:c>
       <x:c r="C225" t="str">
         <x:v>polynomial</x:v>
@@ -3869,10 +3869,10 @@
     </x:row>
     <x:row r="226">
       <x:c r="A226" t="str">
-        <x:v>y=-1851x+4155x^{2}-2495x^{3}+3816x^{4}-653x^{5}-2598x^{6}+C</x:v>
+        <x:v>y=1203x-4481x^{2}-2537x^{3}-4247x^{4}-2172x^{5}-3598x^{6}-710x^{7}+715x^{8}+C</x:v>
       </x:c>
       <x:c r="B226" t="str">
-        <x:v>y^{\prime}=-1851+8310x-7485x^{2}+15264x^{3}-3265x^{4}-15588x^{5}</x:v>
+        <x:v>y^{\prime}=1203-8962x-7611x^{2}-16988x^{3}-10860x^{4}-21588x^{5}-4970x^{6}+5720x^{7}</x:v>
       </x:c>
       <x:c r="C226" t="str">
         <x:v>polynomial</x:v>
@@ -3880,10 +3880,10 @@
     </x:row>
     <x:row r="227">
       <x:c r="A227" t="str">
-        <x:v>y=-3584x-4033x^{2}+4046x^{3}+1027x^{4}-4897x^{5}-4431x^{6}-3779x^{7}+C</x:v>
+        <x:v>y=3789x+973x^{2}-2771x^{3}+636x^{4}+3500x^{5}+C</x:v>
       </x:c>
       <x:c r="B227" t="str">
-        <x:v>y^{\prime}=-3584-8066x+12138x^{2}+4108x^{3}-24485x^{4}-26586x^{5}-26453x^{6}</x:v>
+        <x:v>y^{\prime}=3789+1946x-8313x^{2}+2544x^{3}+17500x^{4}</x:v>
       </x:c>
       <x:c r="C227" t="str">
         <x:v>polynomial</x:v>
@@ -3891,10 +3891,10 @@
     </x:row>
     <x:row r="228">
       <x:c r="A228" t="str">
-        <x:v>y=1203x-4481x^{2}-2537x^{3}-4247x^{4}-2172x^{5}-3598x^{6}-710x^{7}+715x^{8}+C</x:v>
+        <x:v>y=-1724x-1487x^{2}-2980x^{3}+1183x^{4}+821x^{5}+1517x^{6}-3709x^{7}+4173x^{8}+C</x:v>
       </x:c>
       <x:c r="B228" t="str">
-        <x:v>y^{\prime}=1203-8962x-7611x^{2}-16988x^{3}-10860x^{4}-21588x^{5}-4970x^{6}+5720x^{7}</x:v>
+        <x:v>y^{\prime}=-1724-2974x-8940x^{2}+4732x^{3}+4105x^{4}+9102x^{5}-25963x^{6}+33384x^{7}</x:v>
       </x:c>
       <x:c r="C228" t="str">
         <x:v>polynomial</x:v>
@@ -3902,10 +3902,10 @@
     </x:row>
     <x:row r="229">
       <x:c r="A229" t="str">
-        <x:v>y=3789x+973x^{2}-2771x^{3}+636x^{4}+3500x^{5}+C</x:v>
+        <x:v>y=-3223x-3704x^{2}+690x^{3}-4090x^{4}+C</x:v>
       </x:c>
       <x:c r="B229" t="str">
-        <x:v>y^{\prime}=3789+1946x-8313x^{2}+2544x^{3}+17500x^{4}</x:v>
+        <x:v>y^{\prime}=-3223-7408x+2070x^{2}-16360x^{3}</x:v>
       </x:c>
       <x:c r="C229" t="str">
         <x:v>polynomial</x:v>
@@ -3913,10 +3913,10 @@
     </x:row>
     <x:row r="230">
       <x:c r="A230" t="str">
-        <x:v>y=-1724x-1487x^{2}-2980x^{3}+1183x^{4}+821x^{5}+1517x^{6}-3709x^{7}+4173x^{8}+C</x:v>
+        <x:v>y=-4409x-2927x^{2}-3010x^{3}-3999x^{4}+C</x:v>
       </x:c>
       <x:c r="B230" t="str">
-        <x:v>y^{\prime}=-1724-2974x-8940x^{2}+4732x^{3}+4105x^{4}+9102x^{5}-25963x^{6}+33384x^{7}</x:v>
+        <x:v>y^{\prime}=-4409-5854x-9030x^{2}-15996x^{3}</x:v>
       </x:c>
       <x:c r="C230" t="str">
         <x:v>polynomial</x:v>
@@ -3924,10 +3924,10 @@
     </x:row>
     <x:row r="231">
       <x:c r="A231" t="str">
-        <x:v>y=-3223x-3704x^{2}+690x^{3}-4090x^{4}+C</x:v>
+        <x:v>y=-175x-2643x^{2}-3011x^{3}-2316x^{4}-3601x^{5}+2035x^{6}+C</x:v>
       </x:c>
       <x:c r="B231" t="str">
-        <x:v>y^{\prime}=-3223-7408x+2070x^{2}-16360x^{3}</x:v>
+        <x:v>y^{\prime}=-175-5286x-9033x^{2}-9264x^{3}-18005x^{4}+12210x^{5}</x:v>
       </x:c>
       <x:c r="C231" t="str">
         <x:v>polynomial</x:v>
@@ -3935,10 +3935,10 @@
     </x:row>
     <x:row r="232">
       <x:c r="A232" t="str">
-        <x:v>y=-4409x-2927x^{2}-3010x^{3}-3999x^{4}+C</x:v>
+        <x:v>y=1005x-1955x^{2}-4099x^{3}+C</x:v>
       </x:c>
       <x:c r="B232" t="str">
-        <x:v>y^{\prime}=-4409-5854x-9030x^{2}-15996x^{3}</x:v>
+        <x:v>y^{\prime}=1005-3910x-12297x^{2}</x:v>
       </x:c>
       <x:c r="C232" t="str">
         <x:v>polynomial</x:v>
@@ -3946,10 +3946,10 @@
     </x:row>
     <x:row r="233">
       <x:c r="A233" t="str">
-        <x:v>y=-175x-2643x^{2}-3011x^{3}-2316x^{4}-3601x^{5}+2035x^{6}+C</x:v>
+        <x:v>y=-371x+4612x^{2}+4126x^{3}-1745x^{4}-3456x^{5}+C</x:v>
       </x:c>
       <x:c r="B233" t="str">
-        <x:v>y^{\prime}=-175-5286x-9033x^{2}-9264x^{3}-18005x^{4}+12210x^{5}</x:v>
+        <x:v>y^{\prime}=-371+9224x+12378x^{2}-6980x^{3}-17280x^{4}</x:v>
       </x:c>
       <x:c r="C233" t="str">
         <x:v>polynomial</x:v>
@@ -3957,10 +3957,10 @@
     </x:row>
     <x:row r="234">
       <x:c r="A234" t="str">
-        <x:v>y=1005x-1955x^{2}-4099x^{3}+C</x:v>
+        <x:v>y=-4589x+2410x^{2}+3946x^{3}+C</x:v>
       </x:c>
       <x:c r="B234" t="str">
-        <x:v>y^{\prime}=1005-3910x-12297x^{2}</x:v>
+        <x:v>y^{\prime}=-4589+4820x+11838x^{2}</x:v>
       </x:c>
       <x:c r="C234" t="str">
         <x:v>polynomial</x:v>
@@ -3968,10 +3968,10 @@
     </x:row>
     <x:row r="235">
       <x:c r="A235" t="str">
-        <x:v>y=-371x+4612x^{2}+4126x^{3}-1745x^{4}-3456x^{5}+C</x:v>
+        <x:v>y=1331x-2493x^{2}-2681x^{3}+3748x^{4}+C</x:v>
       </x:c>
       <x:c r="B235" t="str">
-        <x:v>y^{\prime}=-371+9224x+12378x^{2}-6980x^{3}-17280x^{4}</x:v>
+        <x:v>y^{\prime}=1331-4986x-8043x^{2}+14992x^{3}</x:v>
       </x:c>
       <x:c r="C235" t="str">
         <x:v>polynomial</x:v>
@@ -3979,10 +3979,10 @@
     </x:row>
     <x:row r="236">
       <x:c r="A236" t="str">
-        <x:v>y=-4589x+2410x^{2}+3946x^{3}+C</x:v>
+        <x:v>y=-1980x-3196x^{2}+2140x^{3}+4911x^{4}+2977x^{5}+2162x^{6}+C</x:v>
       </x:c>
       <x:c r="B236" t="str">
-        <x:v>y^{\prime}=-4589+4820x+11838x^{2}</x:v>
+        <x:v>y^{\prime}=-1980-6392x+6420x^{2}+19644x^{3}+14885x^{4}+12972x^{5}</x:v>
       </x:c>
       <x:c r="C236" t="str">
         <x:v>polynomial</x:v>
@@ -3990,10 +3990,10 @@
     </x:row>
     <x:row r="237">
       <x:c r="A237" t="str">
-        <x:v>y=1331x-2493x^{2}-2681x^{3}+3748x^{4}+C</x:v>
+        <x:v>y=-3169x+531x^{2}+2482x^{3}-281x^{4}-1107x^{5}+C</x:v>
       </x:c>
       <x:c r="B237" t="str">
-        <x:v>y^{\prime}=1331-4986x-8043x^{2}+14992x^{3}</x:v>
+        <x:v>y^{\prime}=-3169+1062x+7446x^{2}-1124x^{3}-5535x^{4}</x:v>
       </x:c>
       <x:c r="C237" t="str">
         <x:v>polynomial</x:v>
@@ -4001,10 +4001,10 @@
     </x:row>
     <x:row r="238">
       <x:c r="A238" t="str">
-        <x:v>y=-1980x-3196x^{2}+2140x^{3}+4911x^{4}+2977x^{5}+2162x^{6}+C</x:v>
+        <x:v>y=-438x-3338x^{2}-3587x^{3}-2137x^{4}-4461x^{5}+C</x:v>
       </x:c>
       <x:c r="B238" t="str">
-        <x:v>y^{\prime}=-1980-6392x+6420x^{2}+19644x^{3}+14885x^{4}+12972x^{5}</x:v>
+        <x:v>y^{\prime}=-438-6676x-10761x^{2}-8548x^{3}-22305x^{4}</x:v>
       </x:c>
       <x:c r="C238" t="str">
         <x:v>polynomial</x:v>
@@ -4012,10 +4012,10 @@
     </x:row>
     <x:row r="239">
       <x:c r="A239" t="str">
-        <x:v>y=-3169x+531x^{2}+2482x^{3}-281x^{4}-1107x^{5}+C</x:v>
+        <x:v>y=-1112x-1757x^{2}+C</x:v>
       </x:c>
       <x:c r="B239" t="str">
-        <x:v>y^{\prime}=-3169+1062x+7446x^{2}-1124x^{3}-5535x^{4}</x:v>
+        <x:v>y^{\prime}=-1112-3514x</x:v>
       </x:c>
       <x:c r="C239" t="str">
         <x:v>polynomial</x:v>
@@ -4023,10 +4023,10 @@
     </x:row>
     <x:row r="240">
       <x:c r="A240" t="str">
-        <x:v>y=-438x-3338x^{2}-3587x^{3}-2137x^{4}-4461x^{5}+C</x:v>
+        <x:v>y=-3128x+667x^{2}+C</x:v>
       </x:c>
       <x:c r="B240" t="str">
-        <x:v>y^{\prime}=-438-6676x-10761x^{2}-8548x^{3}-22305x^{4}</x:v>
+        <x:v>y^{\prime}=-3128+1334x</x:v>
       </x:c>
       <x:c r="C240" t="str">
         <x:v>polynomial</x:v>
@@ -4034,10 +4034,10 @@
     </x:row>
     <x:row r="241">
       <x:c r="A241" t="str">
-        <x:v>y=-1112x-1757x^{2}+C</x:v>
+        <x:v>y=2060x+1991x^{2}-1823x^{3}-1953x^{4}-3926x^{5}+4001x^{6}+3650x^{7}-2140x^{8}+C</x:v>
       </x:c>
       <x:c r="B241" t="str">
-        <x:v>y^{\prime}=-1112-3514x</x:v>
+        <x:v>y^{\prime}=2060+3982x-5469x^{2}-7812x^{3}-19630x^{4}+24006x^{5}+25550x^{6}-17120x^{7}</x:v>
       </x:c>
       <x:c r="C241" t="str">
         <x:v>polynomial</x:v>
@@ -4045,10 +4045,10 @@
     </x:row>
     <x:row r="242">
       <x:c r="A242" t="str">
-        <x:v>y=-3128x+667x^{2}+C</x:v>
+        <x:v>y=2266x+400x^{2}+121x^{3}+4367x^{4}-1162x^{5}-3434x^{6}-4936x^{7}-2236x^{8}+C</x:v>
       </x:c>
       <x:c r="B242" t="str">
-        <x:v>y^{\prime}=-3128+1334x</x:v>
+        <x:v>y^{\prime}=2266+800x+363x^{2}+17468x^{3}-5810x^{4}-20604x^{5}-34552x^{6}-17888x^{7}</x:v>
       </x:c>
       <x:c r="C242" t="str">
         <x:v>polynomial</x:v>
@@ -4056,10 +4056,10 @@
     </x:row>
     <x:row r="243">
       <x:c r="A243" t="str">
-        <x:v>y=2060x+1991x^{2}-1823x^{3}-1953x^{4}-3926x^{5}+4001x^{6}+3650x^{7}-2140x^{8}+C</x:v>
+        <x:v>y=-551x-4445x^{2}-3751x^{3}+C</x:v>
       </x:c>
       <x:c r="B243" t="str">
-        <x:v>y^{\prime}=2060+3982x-5469x^{2}-7812x^{3}-19630x^{4}+24006x^{5}+25550x^{6}-17120x^{7}</x:v>
+        <x:v>y^{\prime}=-551-8890x-11253x^{2}</x:v>
       </x:c>
       <x:c r="C243" t="str">
         <x:v>polynomial</x:v>
@@ -4067,10 +4067,10 @@
     </x:row>
     <x:row r="244">
       <x:c r="A244" t="str">
-        <x:v>y=2266x+400x^{2}+121x^{3}+4367x^{4}-1162x^{5}-3434x^{6}-4936x^{7}-2236x^{8}+C</x:v>
+        <x:v>y=808x+4660x^{2}-3523x^{3}+1037x^{4}+2012x^{5}+C</x:v>
       </x:c>
       <x:c r="B244" t="str">
-        <x:v>y^{\prime}=2266+800x+363x^{2}+17468x^{3}-5810x^{4}-20604x^{5}-34552x^{6}-17888x^{7}</x:v>
+        <x:v>y^{\prime}=808+9320x-10569x^{2}+4148x^{3}+10060x^{4}</x:v>
       </x:c>
       <x:c r="C244" t="str">
         <x:v>polynomial</x:v>
@@ -4078,10 +4078,10 @@
     </x:row>
     <x:row r="245">
       <x:c r="A245" t="str">
-        <x:v>y=-551x-4445x^{2}-3751x^{3}+C</x:v>
+        <x:v>y=4612x-2891x^{2}-2454x^{3}+871x^{4}-3965x^{5}+C</x:v>
       </x:c>
       <x:c r="B245" t="str">
-        <x:v>y^{\prime}=-551-8890x-11253x^{2}</x:v>
+        <x:v>y^{\prime}=4612-5782x-7362x^{2}+3484x^{3}-19825x^{4}</x:v>
       </x:c>
       <x:c r="C245" t="str">
         <x:v>polynomial</x:v>
@@ -4089,10 +4089,10 @@
     </x:row>
     <x:row r="246">
       <x:c r="A246" t="str">
-        <x:v>y=808x+4660x^{2}-3523x^{3}+1037x^{4}+2012x^{5}+C</x:v>
+        <x:v>y=-1950x+1250x^{2}+C</x:v>
       </x:c>
       <x:c r="B246" t="str">
-        <x:v>y^{\prime}=808+9320x-10569x^{2}+4148x^{3}+10060x^{4}</x:v>
+        <x:v>y^{\prime}=-1950+2500x</x:v>
       </x:c>
       <x:c r="C246" t="str">
         <x:v>polynomial</x:v>
@@ -4100,34 +4100,12 @@
     </x:row>
     <x:row r="247">
       <x:c r="A247" t="str">
-        <x:v>y=4612x-2891x^{2}-2454x^{3}+871x^{4}-3965x^{5}+C</x:v>
+        <x:v>y=-2215x-3673x^{2}-2816x^{3}+1737x^{4}+797x^{5}+754x^{6}-1682x^{7}+C</x:v>
       </x:c>
       <x:c r="B247" t="str">
-        <x:v>y^{\prime}=4612-5782x-7362x^{2}+3484x^{3}-19825x^{4}</x:v>
+        <x:v>y^{\prime}=-2215-7346x-8448x^{2}+6948x^{3}+3985x^{4}+4524x^{5}-11774x^{6}</x:v>
       </x:c>
       <x:c r="C247" t="str">
-        <x:v>polynomial</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="248">
-      <x:c r="A248" t="str">
-        <x:v>y=-1950x+1250x^{2}+C</x:v>
-      </x:c>
-      <x:c r="B248" t="str">
-        <x:v>y^{\prime}=-1950+2500x</x:v>
-      </x:c>
-      <x:c r="C248" t="str">
-        <x:v>polynomial</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="249">
-      <x:c r="A249" t="str">
-        <x:v>y=-2215x-3673x^{2}-2816x^{3}+1737x^{4}+797x^{5}+754x^{6}-1682x^{7}+C</x:v>
-      </x:c>
-      <x:c r="B249" t="str">
-        <x:v>y^{\prime}=-2215-7346x-8448x^{2}+6948x^{3}+3985x^{4}+4524x^{5}-11774x^{6}</x:v>
-      </x:c>
-      <x:c r="C249" t="str">
         <x:v>polynomial</x:v>
       </x:c>
     </x:row>
